--- a/result/52w_global_model_results.xlsx
+++ b/result/52w_global_model_results.xlsx
@@ -55,16 +55,16 @@
     <t>ExtraTreeRegressor</t>
   </si>
   <si>
+    <t>Darts</t>
+  </si>
+  <si>
+    <t>pmdarima</t>
+  </si>
+  <si>
+    <t>RandomForestRegressor</t>
+  </si>
+  <si>
     <t>BayesianRidge</t>
-  </si>
-  <si>
-    <t>Darts</t>
-  </si>
-  <si>
-    <t>pmdarima</t>
-  </si>
-  <si>
-    <t>RandomForestRegressor</t>
   </si>
   <si>
     <t>DecisionTreeRegressor</t>
@@ -605,19 +605,13 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>0.4266959556695533</v>
+        <v>0.7882718780155274</v>
       </c>
       <c r="C9">
-        <v>82928.12003464252</v>
+        <v>6093988</v>
       </c>
       <c r="D9">
-        <v>0.3381583690643311</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
+        <v>0.02279233932495117</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -625,13 +619,13 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>0.7882718780155274</v>
+        <v>0.9821999668657048</v>
       </c>
       <c r="C10">
-        <v>6093988</v>
+        <v>7593211.147844728</v>
       </c>
       <c r="D10">
-        <v>0.02279233932495117</v>
+        <v>94.80809473991394</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -639,13 +633,19 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>0.9821999668657048</v>
+        <v>1.071999042445439</v>
       </c>
       <c r="C11">
-        <v>7593211.147844728</v>
+        <v>86605.87000000011</v>
       </c>
       <c r="D11">
-        <v>94.80809473991394</v>
+        <v>13.01693916320801</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -653,13 +653,13 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>1.071999042445439</v>
+        <v>1.342603894190321</v>
       </c>
       <c r="C12">
-        <v>86605.87000000011</v>
+        <v>415075.9962879494</v>
       </c>
       <c r="D12">
-        <v>13.01693916320801</v>
+        <v>0.225989818572998</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
